--- a/data/trans_orig/P2A_fisi_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P2A_fisi_R-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>696</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8113</t>
+          <t>8697</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76160</t>
+          <t>75921</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64842</t>
+          <t>64973</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70938</t>
+          <t>70941</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>143979</t>
+          <t>143395</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150678</t>
+          <t>150735</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5381</t>
+          <t>4840</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>4835</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7311</t>
+          <t>7543</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63306</t>
+          <t>63847</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>62656</t>
+          <t>62650</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>128861</t>
+          <t>128629</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>135015</t>
+          <t>134902</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>614</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>772</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6860</t>
+          <t>6497</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55103</t>
+          <t>54320</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78421</t>
+          <t>78378</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>83334</t>
+          <t>83330</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135329</t>
+          <t>135692</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141415</t>
+          <t>141417</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10350</t>
+          <t>10157</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11852</t>
+          <t>11605</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>146538</t>
+          <t>147278</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>138212</t>
+          <t>138405</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>146299</t>
+          <t>145980</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>288006</t>
+          <t>288253</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>296567</t>
+          <t>296473</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>791</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>8802</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>3726</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13052</t>
+          <t>12746</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61519</t>
+          <t>62118</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68338</t>
+          <t>68332</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75048</t>
+          <t>75728</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>82539</t>
+          <t>82616</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>140600</t>
+          <t>140906</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>149670</t>
+          <t>149926</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>2942</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6066</t>
+          <t>5863</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>696</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>71535</t>
+          <t>71928</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>66326</t>
+          <t>66529</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>71750</t>
+          <t>71753</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>140966</t>
+          <t>141215</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>146564</t>
+          <t>146566</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>15464</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11828</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>26620</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20228</t>
+          <t>19520</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37024</t>
+          <t>36032</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>488046</t>
+          <t>487211</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>497727</t>
+          <t>497603</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>502984</t>
+          <t>501929</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>516721</t>
+          <t>516409</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>994201</t>
+          <t>995193</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1010997</t>
+          <t>1011705</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>4835</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>726</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56922</t>
+          <t>57235</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68262</t>
+          <t>68575</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>128294</t>
+          <t>127880</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>133889</t>
+          <t>133905</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>4678</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5417</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>785</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60316</t>
+          <t>60701</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63109</t>
+          <t>63492</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>126853</t>
+          <t>127328</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>133117</t>
+          <t>133120</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4551</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>9372</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61972</t>
+          <t>62507</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>60704</t>
+          <t>60114</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67191</t>
+          <t>66640</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>125721</t>
+          <t>125115</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>132525</t>
+          <t>132448</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7884</t>
+          <t>7833</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10033</t>
+          <t>10144</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>5155</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14901</t>
+          <t>15016</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>128596</t>
+          <t>128647</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135318</t>
+          <t>135285</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>151331</t>
+          <t>151220</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>158778</t>
+          <t>158666</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>282943</t>
+          <t>282828</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>292859</t>
+          <t>292689</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>996</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7615</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7322</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3095</t>
+          <t>3311</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12068</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86249</t>
+          <t>85836</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>92710</t>
+          <t>92455</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>84686</t>
+          <t>84365</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90669</t>
+          <t>90672</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>173391</t>
+          <t>173748</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>182364</t>
+          <t>182148</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>677</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>6226</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7432</t>
+          <t>7821</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11183</t>
+          <t>12096</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>46862</t>
+          <t>47685</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>53203</t>
+          <t>53234</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>66606</t>
+          <t>66217</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>72716</t>
+          <t>72661</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>116766</t>
+          <t>115853</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>124650</t>
+          <t>124634</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>8595</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21328</t>
+          <t>20541</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13082</t>
+          <t>13216</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26457</t>
+          <t>27261</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24529</t>
+          <t>24398</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42798</t>
+          <t>42589</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>455637</t>
+          <t>456424</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>468548</t>
+          <t>468370</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>510853</t>
+          <t>510049</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>524228</t>
+          <t>524094</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>971477</t>
+          <t>971686</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>989746</t>
+          <t>989877</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6806</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8946</t>
+          <t>8827</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58025</t>
+          <t>58057</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72654</t>
+          <t>71969</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>134139</t>
+          <t>134258</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>142484</t>
+          <t>142485</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>4375</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,44 +6366,44 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5375</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
           <t>5,78%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5392</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>5,79%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7188</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77554</t>
+          <t>77936</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6474,49 +6474,49 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>94,68%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>91986</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>87692</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>93067</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>98,84%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>94,22%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>91986</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>87675</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>93067</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,84%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>94,21%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>254</t>
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>168190</t>
+          <t>168297</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>174735</t>
+          <t>174737</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>602</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>729</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>9375</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44753</t>
+          <t>44227</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48620</t>
+          <t>48622</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54052</t>
+          <t>54114</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60359</t>
+          <t>60282</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>101267</t>
+          <t>100859</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>108319</t>
+          <t>108139</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1557</t>
+          <t>1568</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>9057</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9189</t>
+          <t>8851</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4601</t>
+          <t>4463</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15068</t>
+          <t>14265</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>156381</t>
+          <t>156740</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>164240</t>
+          <t>164229</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>161694</t>
+          <t>162032</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>169084</t>
+          <t>169356</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>321612</t>
+          <t>322415</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>332079</t>
+          <t>332217</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7593</t>
+          <t>7671</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6287</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2468</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10422</t>
+          <t>10175</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>93986</t>
+          <t>93908</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>100337</t>
+          <t>100322</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>92866</t>
+          <t>93330</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>98498</t>
+          <t>98507</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>190310</t>
+          <t>190557</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>198264</t>
+          <t>198089</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>562</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>56649</t>
+          <t>55858</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64228</t>
+          <t>63241</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>122803</t>
+          <t>122557</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>127589</t>
+          <t>127597</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8712</t>
+          <t>8777</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21369</t>
+          <t>20998</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7733</t>
+          <t>7420</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19740</t>
+          <t>20023</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19018</t>
+          <t>17854</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37158</t>
+          <t>35661</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>502707</t>
+          <t>503078</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>515364</t>
+          <t>515299</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>550452</t>
+          <t>550169</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>562459</t>
+          <t>562772</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1057110</t>
+          <t>1058607</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1075250</t>
+          <t>1076414</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>557</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5050</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9168</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2373</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11345</t>
+          <t>10532</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>99412</t>
+          <t>99465</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103903</t>
+          <t>103905</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>127740</t>
+          <t>128073</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135856</t>
+          <t>135903</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>230025</t>
+          <t>230838</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>238997</t>
+          <t>239178</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>987</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1624</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9078</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13034</t>
+          <t>12459</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88689</t>
+          <t>87913</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93955</t>
+          <t>93694</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>86495</t>
+          <t>86401</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>93981</t>
+          <t>93949</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>177220</t>
+          <t>177795</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>186668</t>
+          <t>186908</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>747</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>6412</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8698</t>
+          <t>8569</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2911</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11466</t>
+          <t>11765</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45454</t>
+          <t>45449</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51086</t>
+          <t>51114</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55155</t>
+          <t>55284</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62650</t>
+          <t>62517</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>104248</t>
+          <t>103949</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>112803</t>
+          <t>112698</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>4388</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15718</t>
+          <t>15157</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8760</t>
+          <t>7932</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30766</t>
+          <t>29276</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14605</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38688</t>
+          <t>41567</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>203107</t>
+          <t>203668</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>214111</t>
+          <t>214437</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>187506</t>
+          <t>188996</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>209512</t>
+          <t>210340</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>398409</t>
+          <t>395530</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>422492</t>
+          <t>421244</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6935</t>
+          <t>7390</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17998</t>
+          <t>18782</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6612</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18507</t>
+          <t>18900</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16516</t>
+          <t>16249</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33107</t>
+          <t>32645</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>101430</t>
+          <t>100646</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>112493</t>
+          <t>112038</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>144110</t>
+          <t>143717</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>156005</t>
+          <t>155882</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>248938</t>
+          <t>249400</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>265529</t>
+          <t>265796</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>9926</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13132</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7684</t>
+          <t>7583</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19141</t>
+          <t>18710</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>58947</t>
+          <t>58969</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66375</t>
+          <t>66292</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>58871</t>
+          <t>60131</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68727</t>
+          <t>68754</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>121757</t>
+          <t>122188</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>133214</t>
+          <t>133315</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25574</t>
+          <t>24959</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45524</t>
+          <t>45215</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33944</t>
+          <t>33521</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61538</t>
+          <t>61740</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63341</t>
+          <t>64911</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>99118</t>
+          <t>98632</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>612629</t>
+          <t>612938</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>632579</t>
+          <t>633194</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>687687</t>
+          <t>687485</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>715281</t>
+          <t>715704</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1308260</t>
+          <t>1308746</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1344037</t>
+          <t>1342467</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
